--- a/office/data/学生成绩.xlsx
+++ b/office/data/学生成绩.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\glpla.github.io\office\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD12BFF1-8ABA-4282-84C7-83964F620413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2996BD-79B2-40D3-8C4A-D47CC9F220BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
   <sheets>
-    <sheet name="原始数据" sheetId="1" r:id="rId1"/>
+    <sheet name="学生成绩" sheetId="1" r:id="rId1"/>
+    <sheet name="销售记录" sheetId="3" r:id="rId2"/>
+    <sheet name="工资表" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">原始数据!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">学生成绩!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,71 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
-  <si>
-    <t>sn001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn002</t>
-  </si>
-  <si>
-    <t>cq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn003</t>
-  </si>
-  <si>
-    <t>sz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn004</t>
-  </si>
-  <si>
-    <t>sh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn005</t>
-  </si>
-  <si>
-    <t>nj</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn006</t>
-  </si>
-  <si>
-    <t>xm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn007</t>
-  </si>
-  <si>
-    <t>fs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn008</t>
-  </si>
-  <si>
-    <t>hk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn009</t>
-  </si>
-  <si>
-    <t>dg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="125">
   <si>
     <t>学号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,48 +58,6 @@
   <si>
     <t>公共体育</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn010</t>
-  </si>
-  <si>
-    <t>km</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn011</t>
-  </si>
-  <si>
-    <t>lz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn012</t>
-  </si>
-  <si>
-    <t>sn013</t>
-  </si>
-  <si>
-    <t>hz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zj</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn014</t>
-  </si>
-  <si>
-    <t>sy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sn015</t>
   </si>
   <si>
     <t>参加考试人数</t>
@@ -256,12 +152,309 @@
 5. 百分比保留小数点后2位，其它数字为整数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>5/7/2021</t>
+  </si>
+  <si>
+    <t>2/2/2021</t>
+  </si>
+  <si>
+    <t>3/3/2021</t>
+  </si>
+  <si>
+    <t>6/4/2021</t>
+  </si>
+  <si>
+    <t>7/5/2021</t>
+  </si>
+  <si>
+    <t>1/6/2021</t>
+  </si>
+  <si>
+    <t>2/7/2021</t>
+  </si>
+  <si>
+    <t>5/8/2021</t>
+  </si>
+  <si>
+    <t>5/9/2021</t>
+  </si>
+  <si>
+    <t>4/10/2021</t>
+  </si>
+  <si>
+    <t>6/24/2021</t>
+  </si>
+  <si>
+    <t>6/12/2021</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>水果</t>
+  </si>
+  <si>
+    <t>蔬菜</t>
+  </si>
+  <si>
+    <t>菠萝</t>
+  </si>
+  <si>
+    <t>奶酪</t>
+  </si>
+  <si>
+    <t>牛奶</t>
+  </si>
+  <si>
+    <t>芒果</t>
+  </si>
+  <si>
+    <t>苹果</t>
+  </si>
+  <si>
+    <t>茄子</t>
+  </si>
+  <si>
+    <t>黄油</t>
+  </si>
+  <si>
+    <t>花椰菜</t>
+  </si>
+  <si>
+    <t>乳制品</t>
+  </si>
+  <si>
+    <t>食品</t>
+  </si>
+  <si>
+    <t>类别</t>
+  </si>
+  <si>
+    <t>销售额</t>
+  </si>
+  <si>
+    <t>白土豆</t>
+  </si>
+  <si>
+    <t>葡萄</t>
+  </si>
+  <si>
+    <t>橙子</t>
+  </si>
+  <si>
+    <t>职工编号</t>
+  </si>
+  <si>
+    <t>职工姓名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>职称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本工资</t>
+  </si>
+  <si>
+    <t>岗位津贴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水电费</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>房租</t>
+  </si>
+  <si>
+    <t>实际收入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>张京平</t>
+  </si>
+  <si>
+    <t>副教授</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>何立立</t>
+  </si>
+  <si>
+    <t>讲师</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>方洪海</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>李宇红</t>
+  </si>
+  <si>
+    <t>教授</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>田皎皎</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>田立萍</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>甘小间</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>戴江宁</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>李洪文</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教授</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>徐万万</t>
+  </si>
+  <si>
+    <t>陈素梅</t>
+  </si>
+  <si>
+    <t>程美娟</t>
+  </si>
+  <si>
+    <t>李金威</t>
+  </si>
+  <si>
+    <t>林艳芳</t>
+  </si>
+  <si>
+    <t>黄健</t>
+  </si>
+  <si>
+    <t>李健威</t>
+  </si>
+  <si>
+    <t>黄欣欣</t>
+  </si>
+  <si>
+    <t>黄艳芳</t>
+  </si>
+  <si>
+    <t>黄怡</t>
+  </si>
+  <si>
+    <t>梁敏红</t>
+  </si>
+  <si>
+    <t>谢书林</t>
+  </si>
+  <si>
+    <t>曾诚</t>
+  </si>
+  <si>
+    <t>樊刚正</t>
+  </si>
+  <si>
+    <t>李翠玲</t>
+  </si>
+  <si>
+    <t>李健</t>
+  </si>
+  <si>
+    <t>李霖明</t>
+  </si>
+  <si>
+    <t>李敏颖</t>
+  </si>
+  <si>
+    <t>03101001</t>
+  </si>
+  <si>
+    <t>03101002</t>
+  </si>
+  <si>
+    <t>03101003</t>
+  </si>
+  <si>
+    <t>03101004</t>
+  </si>
+  <si>
+    <t>03101005</t>
+  </si>
+  <si>
+    <t>03101006</t>
+  </si>
+  <si>
+    <t>03101007</t>
+  </si>
+  <si>
+    <t>03101008</t>
+  </si>
+  <si>
+    <t>03101009</t>
+  </si>
+  <si>
+    <t>03101010</t>
+  </si>
+  <si>
+    <t>03101011</t>
+  </si>
+  <si>
+    <t>03101012</t>
+  </si>
+  <si>
+    <t>03101013</t>
+  </si>
+  <si>
+    <t>03101014</t>
+  </si>
+  <si>
+    <t>03101015</t>
+  </si>
+  <si>
+    <t>03101016</t>
+  </si>
+  <si>
+    <t>03101017</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,6 +469,12 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -656,64 +855,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE67399F-CC12-4ABD-9F7C-F6EE52160CF4}">
-  <dimension ref="A1:T27"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T31"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9" customWidth="1"/>
+    <col min="15" max="15" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="C2">
         <v>18</v>
@@ -731,12 +928,12 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="C3">
         <v>19</v>
@@ -754,24 +951,24 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="O3" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="P3" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="S3" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="T3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="C4">
         <v>18</v>
@@ -792,18 +989,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="S4">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -824,18 +1021,18 @@
         <v>60</v>
       </c>
       <c r="P5" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="S5">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="C6">
         <v>17</v>
@@ -856,18 +1053,18 @@
         <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="S6">
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="C7">
         <v>17</v>
@@ -888,18 +1085,18 @@
         <v>80</v>
       </c>
       <c r="P7" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="S7">
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="C8">
         <v>18</v>
@@ -920,15 +1117,15 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="C9">
         <v>17</v>
@@ -946,12 +1143,12 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="C10">
         <v>17</v>
@@ -969,12 +1166,12 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>18</v>
@@ -991,12 +1188,12 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="C12">
         <v>20</v>
@@ -1013,12 +1210,12 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="C13">
         <v>17</v>
@@ -1035,12 +1232,12 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="C14">
         <v>18</v>
@@ -1057,12 +1254,12 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="C15">
         <v>17</v>
@@ -1079,12 +1276,12 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="C16">
         <v>17</v>
@@ -1101,72 +1298,112 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D22" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D23" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D25" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="27" spans="1:11" ht="93" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17">
+        <v>19</v>
+      </c>
+      <c r="D17">
+        <v>97</v>
+      </c>
+      <c r="E17">
+        <v>94</v>
+      </c>
+      <c r="F17">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18">
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <v>96</v>
+      </c>
+      <c r="E18">
+        <v>93</v>
+      </c>
+      <c r="F18">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="2"/>
+    </row>
+    <row r="31" spans="1:11" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
@@ -1176,4 +1413,481 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43A4D9D-2C34-46F9-8998-D6D5D69FC8F7}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13">
+        <v>2200</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D14">
+    <sortCondition ref="B2:B14"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC66C260-99D9-44C3-B324-76C50FC519FC}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2">
+        <v>4700</v>
+      </c>
+      <c r="F2">
+        <v>103</v>
+      </c>
+      <c r="G2">
+        <v>800</v>
+      </c>
+      <c r="H2">
+        <f>D2+E2-(F2+G2)</f>
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3">
+        <v>3200</v>
+      </c>
+      <c r="F3">
+        <v>205</v>
+      </c>
+      <c r="G3">
+        <v>500</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H11" si="0">D3+E3-(F3+G3)</f>
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4">
+        <v>3400</v>
+      </c>
+      <c r="F4">
+        <v>162</v>
+      </c>
+      <c r="G4">
+        <v>800</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5">
+        <v>5000</v>
+      </c>
+      <c r="F5">
+        <v>95.5</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>3904.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6">
+        <v>4500</v>
+      </c>
+      <c r="F6">
+        <v>100.5</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>3399.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7">
+        <v>3800</v>
+      </c>
+      <c r="F7">
+        <v>150.30000305175781</v>
+      </c>
+      <c r="G7">
+        <v>800</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>2849.6999969482422</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8">
+        <v>4300</v>
+      </c>
+      <c r="F8">
+        <v>110.5</v>
+      </c>
+      <c r="G8">
+        <v>480</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>3709.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9">
+        <v>4500</v>
+      </c>
+      <c r="F9">
+        <v>98.5</v>
+      </c>
+      <c r="G9">
+        <v>900</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>3501.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10">
+        <v>5350</v>
+      </c>
+      <c r="F10">
+        <v>154</v>
+      </c>
+      <c r="G10">
+        <v>600</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11">
+        <v>3700</v>
+      </c>
+      <c r="F11">
+        <v>110.19999694824219</v>
+      </c>
+      <c r="G11">
+        <v>800</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>2789.8000030517578</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/office/data/学生成绩.xlsx
+++ b/office/data/学生成绩.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\office\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2996BD-79B2-40D3-8C4A-D47CC9F220BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF82A91D-54F8-4A91-B9FF-27D7FC2222F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E5A61E7-CF82-4D7E-B994-D412ADB0B79D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="108">
   <si>
     <t>学号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,14 +60,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>参加考试人数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>班级总人数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>总分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,67 +72,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>平均成绩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>平均成绩最高分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>平均成绩最低分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考勤率%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>及格率%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不及格率%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>排名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不及格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>及格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>良好</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优秀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>区间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>评定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>边界值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -485,32 +417,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -519,17 +431,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -870,7 +776,7 @@
     <col min="20" max="20" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -889,28 +795,28 @@
       <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>9</v>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
       </c>
       <c r="I1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>18</v>
@@ -924,16 +830,23 @@
       <c r="F2">
         <v>50</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="G2">
+        <f>SUM(D2:F2)</f>
+        <v>150</v>
+      </c>
+      <c r="H2" s="1">
+        <f>AVERAGE(D2:F2)</f>
+        <v>50</v>
+      </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C3">
         <v>19</v>
@@ -947,28 +860,23 @@
       <c r="F3">
         <v>85</v>
       </c>
-      <c r="H3" s="1"/>
+      <c r="G3">
+        <f t="shared" ref="G3:G18" si="0">SUM(D3:F3)</f>
+        <v>232</v>
+      </c>
+      <c r="H3" s="1">
+        <f t="shared" ref="H3:H18" si="1">AVERAGE(D3:F3)</f>
+        <v>77.333333333333329</v>
+      </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="O3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" t="s">
-        <v>25</v>
-      </c>
-      <c r="S3" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C4">
         <v>18</v>
@@ -982,25 +890,23 @@
       <c r="F4">
         <v>60</v>
       </c>
-      <c r="H4" s="1"/>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>227</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="1"/>
+        <v>75.666666666666671</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4" t="s">
-        <v>19</v>
-      </c>
-      <c r="S4">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -1014,25 +920,23 @@
       <c r="F5">
         <v>90</v>
       </c>
-      <c r="H5" s="1"/>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>262</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="1"/>
+        <v>87.333333333333329</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="O5">
-        <v>60</v>
-      </c>
-      <c r="P5" t="s">
-        <v>20</v>
-      </c>
-      <c r="S5">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C6">
         <v>17</v>
@@ -1046,25 +950,23 @@
       <c r="F6">
         <v>88</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>218</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="1"/>
+        <v>72.666666666666671</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="O6">
-        <v>70</v>
-      </c>
-      <c r="P6" t="s">
-        <v>21</v>
-      </c>
-      <c r="S6">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" t="s">
-        <v>96</v>
       </c>
       <c r="C7">
         <v>17</v>
@@ -1078,25 +980,23 @@
       <c r="F7">
         <v>100</v>
       </c>
-      <c r="H7" s="1"/>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>251</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="1"/>
+        <v>83.666666666666671</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="O7">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s">
         <v>80</v>
-      </c>
-      <c r="P7" t="s">
-        <v>22</v>
-      </c>
-      <c r="S7">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" t="s">
-        <v>97</v>
       </c>
       <c r="C8">
         <v>18</v>
@@ -1110,22 +1010,23 @@
       <c r="F8">
         <v>99</v>
       </c>
-      <c r="H8" s="1"/>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>268</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="1"/>
+        <v>89.333333333333329</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="O8">
-        <v>90</v>
-      </c>
-      <c r="P8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C9">
         <v>17</v>
@@ -1139,16 +1040,23 @@
       <c r="F9">
         <v>91</v>
       </c>
-      <c r="H9" s="1"/>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>251</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="1"/>
+        <v>83.666666666666671</v>
+      </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C10">
         <v>17</v>
@@ -1162,16 +1070,23 @@
       <c r="F10">
         <v>77</v>
       </c>
-      <c r="H10" s="1"/>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="1"/>
+        <v>76.666666666666671</v>
+      </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C11">
         <v>18</v>
@@ -1185,15 +1100,23 @@
       <c r="F11">
         <v>89</v>
       </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C12">
         <v>20</v>
@@ -1207,15 +1130,23 @@
       <c r="F12">
         <v>81</v>
       </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>221</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="1"/>
+        <v>73.666666666666671</v>
+      </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C13">
         <v>17</v>
@@ -1229,15 +1160,23 @@
       <c r="F13">
         <v>69</v>
       </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>231</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C14">
         <v>18</v>
@@ -1251,15 +1190,23 @@
       <c r="F14">
         <v>91</v>
       </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>253</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="1"/>
+        <v>84.333333333333329</v>
+      </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="C15">
         <v>17</v>
@@ -1273,15 +1220,23 @@
       <c r="F15">
         <v>79</v>
       </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>214</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="1"/>
+        <v>71.333333333333329</v>
+      </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C16">
         <v>17</v>
@@ -1295,15 +1250,23 @@
       <c r="F16">
         <v>90</v>
       </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>248</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="1"/>
+        <v>82.666666666666671</v>
+      </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C17">
         <v>19</v>
@@ -1317,13 +1280,21 @@
       <c r="F17">
         <v>96</v>
       </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>287</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="1"/>
+        <v>95.666666666666671</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -1337,69 +1308,29 @@
       <c r="F18">
         <v>98</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="3"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="3"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="2"/>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>287</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="1"/>
+        <v>95.666666666666671</v>
+      </c>
     </row>
     <row r="31" spans="1:11" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
+      <c r="A31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1426,27 +1357,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>2500</v>
@@ -1454,13 +1385,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>150</v>
@@ -1468,13 +1399,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>3000</v>
@@ -1482,13 +1413,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>4000</v>
@@ -1496,13 +1427,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>2700</v>
@@ -1510,13 +1441,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>600</v>
@@ -1524,13 +1455,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>5000</v>
@@ -1538,13 +1469,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>3500</v>
@@ -1552,13 +1483,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>2600</v>
@@ -1566,13 +1497,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>700</v>
@@ -1580,13 +1511,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>1200</v>
@@ -1594,13 +1525,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>2200</v>
@@ -1622,39 +1553,39 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H1" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D2">
         <v>4700</v>
@@ -1672,13 +1603,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D3">
         <v>3200</v>
@@ -1696,13 +1627,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D4">
         <v>3400</v>
@@ -1720,13 +1651,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D5">
         <v>5000</v>
@@ -1744,13 +1675,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>4500</v>
@@ -1768,13 +1699,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D7">
         <v>3800</v>
@@ -1792,13 +1723,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D8">
         <v>4300</v>
@@ -1816,13 +1747,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>4500</v>
@@ -1840,13 +1771,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="D10">
         <v>5350</v>
@@ -1864,13 +1795,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D11">
         <v>3700</v>
